--- a/data/derived_data/2_RarefyData/Dataset_2/ps_16S_filt_Dataset_2_otu_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_2/ps_16S_filt_Dataset_2_otu_table.xlsx
@@ -12,11 +12,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">LC_121</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC_122</t>
   </si>
   <si>
@@ -35,6 +38,9 @@
     <t xml:space="preserve">LC_127</t>
   </si>
   <si>
+    <t xml:space="preserve">LC_128</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC_130</t>
   </si>
   <si>
@@ -53,6 +59,9 @@
     <t xml:space="preserve">LC_152</t>
   </si>
   <si>
+    <t xml:space="preserve">LC_153</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC_154</t>
   </si>
   <si>
@@ -65,9 +74,6 @@
     <t xml:space="preserve">LC_157</t>
   </si>
   <si>
-    <t xml:space="preserve">MS_006</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_008</t>
   </si>
   <si>
@@ -80,6 +86,9 @@
     <t xml:space="preserve">MS_013</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_014</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_015</t>
   </si>
   <si>
@@ -101,6 +110,9 @@
     <t xml:space="preserve">MS_021</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_022</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_055</t>
   </si>
   <si>
@@ -119,6 +131,12 @@
     <t xml:space="preserve">MS_060</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_064</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_065</t>
   </si>
   <si>
@@ -152,6 +170,9 @@
     <t xml:space="preserve">MS_180</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_181</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_183</t>
   </si>
   <si>
@@ -203,37 +224,106 @@
     <t xml:space="preserve">MS_204</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_11</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_113</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_1389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_1533</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_16</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_20</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_3028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_320</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_337</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_34</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_35</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_449</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_47</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_5</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_53</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_55</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_93</t>
   </si>
 </sst>
 </file>
@@ -752,10 +842,31 @@
       <c r="BK1" t="s">
         <v>62</v>
       </c>
+      <c r="BL1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -764,61 +875,61 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>287</v>
+        <v>370</v>
       </c>
       <c r="F2" t="n">
-        <v>107</v>
+        <v>1100</v>
       </c>
       <c r="G2" t="n">
-        <v>549</v>
+        <v>332</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>871</v>
       </c>
       <c r="U2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -833,13 +944,13 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -887,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -941,48 +1052,69 @@
         <v>0</v>
       </c>
       <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B3" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>14325</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1105</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8408</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>555</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>11897</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>7877</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -991,16 +1123,16 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>734</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -1009,40 +1141,40 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>738</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -1051,16 +1183,16 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>249</v>
+        <v>2085</v>
       </c>
       <c r="AK3" t="n">
-        <v>260</v>
+        <v>3980</v>
       </c>
       <c r="AL3" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1075,25 +1207,25 @@
         <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2677</v>
       </c>
       <c r="AS3" t="n">
-        <v>2</v>
+        <v>1994</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1078</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>59756</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>48411</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -1102,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1807</v>
+        <v>757</v>
       </c>
       <c r="BB3" t="n">
-        <v>2248</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
@@ -1114,30 +1246,51 @@
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
       <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1034</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>683</v>
+      </c>
+      <c r="BR3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -1149,16 +1302,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1167,16 +1320,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1194,19 +1347,19 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1224,49 +1377,49 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>1597</v>
+        <v>56</v>
       </c>
       <c r="AG4" t="n">
-        <v>2432</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>844</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1164</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1633</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1737</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>547</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7639</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>7614</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -1287,16 +1440,16 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>993</v>
+        <v>3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1509</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>2634</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>2531</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
@@ -1317,18 +1470,39 @@
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>3022</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>2324</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>3040</v>
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -1382,13 +1556,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1397,129 +1571,150 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>41</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>12</v>
       </c>
-      <c r="AE5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BK5" t="n">
+      <c r="BR5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -1570,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1636,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>18898</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>23829</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -1648,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
@@ -1669,10 +1864,10 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -1705,12 +1900,33 @@
         <v>0</v>
       </c>
       <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -1761,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1776,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>5422</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2174</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1815,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1848,16 +2064,16 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>679</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1171</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -1896,72 +2112,93 @@
         <v>0</v>
       </c>
       <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="D8" t="n">
-        <v>2812</v>
+        <v>48</v>
       </c>
       <c r="E8" t="n">
-        <v>1985</v>
+        <v>14325</v>
       </c>
       <c r="F8" t="n">
-        <v>469</v>
+        <v>1105</v>
       </c>
       <c r="G8" t="n">
-        <v>185</v>
+        <v>8408</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>808</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L8" t="n">
-        <v>4220</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1936</v>
+        <v>555</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>11897</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>7877</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1808</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1970,47 +2207,47 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="AA8" t="n">
+        <v>738</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>96</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>39</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
         <v>12</v>
       </c>
-      <c r="AB8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
@@ -2024,16 +2261,16 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
@@ -2051,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -2069,7 +2306,7 @@
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -2078,21 +2315,42 @@
         <v>0</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1807</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2248</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
       </c>
       <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -2101,16 +2359,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>821</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1416</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2145</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>892</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -2125,10 +2383,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3226</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2140,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1211</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2197,16 +2455,16 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1597</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2432</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -2215,31 +2473,31 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>844</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1164</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1633</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1737</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>547</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>7639</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>7614</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -2263,27 +2521,48 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>993</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1509</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>2634</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2531</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>3022</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>2324</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>3040</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -2298,19 +2577,19 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>9657</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>24152</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>27867</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2756</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2319,13 +2598,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>8970</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>27094</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>765</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2337,144 +2616,165 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>9494</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>7886</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3128</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>9101</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>7915</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>305</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>30403</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>26298</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4184</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>35791</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>53842</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>18643</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>28783</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>20006</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>29098</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>51239</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>51508</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>42229</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>41863</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>14131</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>12953</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>3367</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>27658</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>21860</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>4819</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>5749</v>
       </c>
       <c r="AU10" t="n">
-        <v>45002</v>
+        <v>6090</v>
       </c>
       <c r="AV10" t="n">
-        <v>49019</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>3870</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>6039</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>5014</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7231</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>8316</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>8536</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>101998</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>118872</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>82147</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>82979</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>21830</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="n">
-        <v>17668</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>34179</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>26907</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>4487</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>2982</v>
+      </c>
+      <c r="BR10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -2483,16 +2783,16 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1978</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -2504,13 +2804,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5313</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2522,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2552,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2564,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2585,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -2660,12 +2960,33 @@
         <v>0</v>
       </c>
       <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -2689,169 +3010,5066 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>12372</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>5495</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="n">
+        <v>76</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>624</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>876</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1622</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1026</v>
+      </c>
+      <c r="J16" t="n">
+        <v>60</v>
+      </c>
+      <c r="K16" t="n">
+        <v>735</v>
+      </c>
+      <c r="L16" t="n">
+        <v>977</v>
+      </c>
+      <c r="M16" t="n">
+        <v>89</v>
+      </c>
+      <c r="N16" t="n">
+        <v>296</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2376</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>784</v>
+      </c>
+      <c r="R16" t="n">
+        <v>616</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>260</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>122</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1990</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2359</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>332</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>193</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>78</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>3802</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3510</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>70</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>25</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>105</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>54</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>263</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G23" t="n">
+        <v>469</v>
+      </c>
+      <c r="H23" t="n">
+        <v>185</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4220</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1936</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1808</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>98</v>
+      </c>
+      <c r="V24" t="n">
+        <v>26</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>295</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>428</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>35</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1688</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>966</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>388</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>379</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>256</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>274</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>131</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>81</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>821</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1416</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2145</v>
+      </c>
+      <c r="H26" t="n">
+        <v>892</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>894</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3226</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1211</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9657</v>
+      </c>
+      <c r="H27" t="n">
+        <v>24152</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>27867</v>
+      </c>
+      <c r="K27" t="n">
+        <v>408</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2756</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>8970</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>27094</v>
+      </c>
+      <c r="R27" t="n">
+        <v>765</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>9494</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7886</v>
+      </c>
+      <c r="W27" t="n">
+        <v>4320</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3128</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>9101</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>7915</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>305</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>224</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>30403</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>26298</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>4184</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>35791</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>53842</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>18643</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>28783</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>20006</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>29098</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>51239</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>51508</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>42229</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>41863</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>14131</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>12953</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>3367</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>27658</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>21860</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>4819</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>45002</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>49019</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3870</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>6039</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>5014</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>7231</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>8316</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>8536</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>101998</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>118872</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>82147</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>82979</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>21830</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>17668</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>34179</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>26907</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>56</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>16</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>527</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>84</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>262</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>116</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>250</v>
+      </c>
+      <c r="F30" t="n">
+        <v>232</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1978</v>
+      </c>
+      <c r="H30" t="n">
+        <v>42</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>102</v>
+      </c>
+      <c r="O30" t="n">
+        <v>5313</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>550</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>6022</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>227</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
         <v>1011</v>
       </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
         <v>5443</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AI31" t="n">
         <v>5903</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AJ31" t="n">
         <v>531</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AK31" t="n">
         <v>1234</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AL31" t="n">
         <v>12584</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AM31" t="n">
         <v>18432</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
         <v>35030</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AQ31" t="n">
         <v>30247</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AR31" t="n">
         <v>313</v>
       </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
         <v>21002</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AU31" t="n">
         <v>20482</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AV31" t="n">
         <v>17181</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AW31" t="n">
         <v>896</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AX31" t="n">
         <v>814</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AY31" t="n">
         <v>41159</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AZ31" t="n">
         <v>24706</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
         <v>81668</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BC31" t="n">
         <v>85143</v>
       </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
         <v>3249</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BG31" t="n">
         <v>4747</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BH31" t="n">
         <v>13627</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BI31" t="n">
         <v>26315</v>
       </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
+      <c r="BJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL31" t="n">
         <v>62047</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BM31" t="n">
         <v>70932</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BN31" t="n">
         <v>134614</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BO31" t="n">
         <v>105913</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BP31" t="n">
         <v>14686</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BQ31" t="n">
         <v>11344</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BR31" t="n">
         <v>7324</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>527</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>10491</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>13346</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>47</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>52965</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>26861</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>744</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>745</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>747</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>11070</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>9382</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>11389</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>7213</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>307</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>304</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>8344</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>5998</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>150</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>162</v>
+      </c>
+      <c r="F33" t="n">
+        <v>145</v>
+      </c>
+      <c r="G33" t="n">
+        <v>265</v>
+      </c>
+      <c r="H33" t="n">
+        <v>127</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>160</v>
+      </c>
+      <c r="K33" t="n">
+        <v>180</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>182</v>
+      </c>
+      <c r="N33" t="n">
+        <v>60</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>41</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>95</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>168</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>186</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>327</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>112</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>358</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>61</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3037</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3128</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>34266</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>27690</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>2965</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>4755</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>112</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>155</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>5131</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>3470</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>33</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
